--- a/tests/ui_tests/test_e2e_report.xlsx
+++ b/tests/ui_tests/test_e2e_report.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-02 21:33:47</t>
+          <t>2026-04-12 16:43:46</t>
         </is>
       </c>
     </row>
@@ -474,7 +474,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-02 21:33:52</t>
+          <t>2026-04-12 16:43:53</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-02 21:33:56</t>
+          <t>2026-04-12 16:43:57</t>
         </is>
       </c>
     </row>
